--- a/data/base/Backlog_31.xlsx
+++ b/data/base/Backlog_31.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF5C363-A21E-4CFC-878C-3E2A626F236B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F05E56-0DE2-4DB9-9073-33AFEF816113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0EC3D47E-816B-47F5-AFA6-593259B1B5C6}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="SPN" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="30">
   <si>
     <t>Setor</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>Emerson Simette</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -616,7 +619,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -632,19 +635,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="17" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1033,7 +1030,7 @@
     <col min="6" max="6" width="18" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.140625" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="3"/>
@@ -1079,9 +1076,9 @@
         <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="11">
+        <v>19</v>
+      </c>
+      <c r="C2" s="7">
         <v>2026</v>
       </c>
       <c r="D2" s="7">
@@ -1090,22 +1087,22 @@
       <c r="E2" s="8">
         <v>46244</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="8">
         <v>46248</v>
       </c>
       <c r="G2" s="7">
-        <v>20268</v>
-      </c>
-      <c r="H2" s="10">
+        <v>21876</v>
+      </c>
+      <c r="H2" s="9">
         <v>46204</v>
       </c>
       <c r="I2" s="8">
         <v>46244</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1116,7 +1113,7 @@
       <c r="B3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="7">
         <v>2026</v>
       </c>
       <c r="D3" s="7">
@@ -1125,22 +1122,22 @@
       <c r="E3" s="8">
         <v>46244</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="8">
         <v>46248</v>
       </c>
       <c r="G3" s="7">
         <v>20486</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <v>46204</v>
       </c>
       <c r="I3" s="8">
         <v>46244</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1149,9 +1146,9 @@
         <v>11</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="11">
+        <v>14</v>
+      </c>
+      <c r="C4" s="7">
         <v>2026</v>
       </c>
       <c r="D4" s="7">
@@ -1160,22 +1157,22 @@
       <c r="E4" s="8">
         <v>46244</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <v>46248</v>
       </c>
       <c r="G4" s="7">
-        <v>21038</v>
-      </c>
-      <c r="H4" s="10">
+        <v>22080</v>
+      </c>
+      <c r="H4" s="9">
         <v>46204</v>
       </c>
       <c r="I4" s="8">
         <v>46244</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1184,9 +1181,9 @@
         <v>11</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="11">
+        <v>14</v>
+      </c>
+      <c r="C5" s="7">
         <v>2026</v>
       </c>
       <c r="D5" s="7">
@@ -1195,22 +1192,22 @@
       <c r="E5" s="8">
         <v>46244</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>46248</v>
       </c>
       <c r="G5" s="7">
-        <v>21202</v>
-      </c>
-      <c r="H5" s="10">
-        <v>46204</v>
+        <v>22158</v>
+      </c>
+      <c r="H5" s="9">
+        <v>46235</v>
       </c>
       <c r="I5" s="8">
         <v>46244</v>
       </c>
-      <c r="J5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="11" t="s">
+      <c r="J5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1219,9 +1216,9 @@
         <v>11</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="11">
+        <v>14</v>
+      </c>
+      <c r="C6" s="7">
         <v>2026</v>
       </c>
       <c r="D6" s="7">
@@ -1230,22 +1227,22 @@
       <c r="E6" s="8">
         <v>46244</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <v>46248</v>
       </c>
       <c r="G6" s="7">
-        <v>21381</v>
-      </c>
-      <c r="H6" s="10">
-        <v>46204</v>
+        <v>22167</v>
+      </c>
+      <c r="H6" s="9">
+        <v>46235</v>
       </c>
       <c r="I6" s="8">
         <v>46244</v>
       </c>
-      <c r="J6" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="11" t="s">
+      <c r="J6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1254,9 +1251,9 @@
         <v>11</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="11">
+        <v>14</v>
+      </c>
+      <c r="C7" s="7">
         <v>2026</v>
       </c>
       <c r="D7" s="7">
@@ -1265,22 +1262,22 @@
       <c r="E7" s="8">
         <v>46244</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>46248</v>
       </c>
       <c r="G7" s="7">
-        <v>21488</v>
-      </c>
-      <c r="H7" s="10">
-        <v>46204</v>
+        <v>22225</v>
+      </c>
+      <c r="H7" s="9">
+        <v>46235</v>
       </c>
       <c r="I7" s="8">
         <v>46244</v>
       </c>
-      <c r="J7" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="11" t="s">
+      <c r="J7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1289,9 +1286,9 @@
         <v>11</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="11">
+        <v>14</v>
+      </c>
+      <c r="C8" s="7">
         <v>2026</v>
       </c>
       <c r="D8" s="7">
@@ -1300,22 +1297,22 @@
       <c r="E8" s="8">
         <v>46244</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <v>46248</v>
       </c>
       <c r="G8" s="7">
-        <v>21608</v>
-      </c>
-      <c r="H8" s="10">
-        <v>46204</v>
+        <v>22555</v>
+      </c>
+      <c r="H8" s="9">
+        <v>46235</v>
       </c>
       <c r="I8" s="8">
         <v>46244</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1324,9 +1321,9 @@
         <v>11</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="11">
+        <v>14</v>
+      </c>
+      <c r="C9" s="7">
         <v>2026</v>
       </c>
       <c r="D9" s="7">
@@ -1335,22 +1332,22 @@
       <c r="E9" s="8">
         <v>46244</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <v>46248</v>
       </c>
       <c r="G9" s="7">
-        <v>21876</v>
-      </c>
-      <c r="H9" s="10">
-        <v>46204</v>
+        <v>22562</v>
+      </c>
+      <c r="H9" s="9">
+        <v>46235</v>
       </c>
       <c r="I9" s="8">
         <v>46244</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1359,9 +1356,9 @@
         <v>11</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="11">
+        <v>24</v>
+      </c>
+      <c r="C10" s="7">
         <v>2026</v>
       </c>
       <c r="D10" s="7">
@@ -1370,22 +1367,22 @@
       <c r="E10" s="8">
         <v>46244</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <v>46248</v>
       </c>
       <c r="G10" s="7">
-        <v>22080</v>
-      </c>
-      <c r="H10" s="10">
-        <v>46204</v>
+        <v>22140</v>
+      </c>
+      <c r="H10" s="9">
+        <v>46235</v>
       </c>
       <c r="I10" s="8">
         <v>46244</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1394,9 +1391,9 @@
         <v>11</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="11">
+        <v>21</v>
+      </c>
+      <c r="C11" s="7">
         <v>2026</v>
       </c>
       <c r="D11" s="7">
@@ -1405,22 +1402,22 @@
       <c r="E11" s="8">
         <v>46244</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <v>46248</v>
       </c>
       <c r="G11" s="7">
-        <v>22140</v>
-      </c>
-      <c r="H11" s="10">
+        <v>22187</v>
+      </c>
+      <c r="H11" s="9">
         <v>46235</v>
       </c>
       <c r="I11" s="8">
         <v>46244</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1429,9 +1426,9 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="11">
+        <v>21</v>
+      </c>
+      <c r="C12" s="7">
         <v>2026</v>
       </c>
       <c r="D12" s="7">
@@ -1440,22 +1437,22 @@
       <c r="E12" s="8">
         <v>46244</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="8">
         <v>46248</v>
       </c>
       <c r="G12" s="7">
-        <v>22158</v>
-      </c>
-      <c r="H12" s="10">
+        <v>22233</v>
+      </c>
+      <c r="H12" s="9">
         <v>46235</v>
       </c>
       <c r="I12" s="8">
         <v>46244</v>
       </c>
-      <c r="J12" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="11" t="s">
+      <c r="J12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1464,9 +1461,9 @@
         <v>11</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="11">
+        <v>15</v>
+      </c>
+      <c r="C13" s="7">
         <v>2026</v>
       </c>
       <c r="D13" s="7">
@@ -1475,22 +1472,22 @@
       <c r="E13" s="8">
         <v>46244</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="8">
         <v>46248</v>
       </c>
       <c r="G13" s="7">
-        <v>22167</v>
-      </c>
-      <c r="H13" s="10">
-        <v>46235</v>
+        <v>21038</v>
+      </c>
+      <c r="H13" s="9">
+        <v>46204</v>
       </c>
       <c r="I13" s="8">
         <v>46244</v>
       </c>
-      <c r="J13" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K13" s="11" t="s">
+      <c r="J13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1499,9 +1496,9 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="11">
+        <v>13</v>
+      </c>
+      <c r="C14" s="7">
         <v>2026</v>
       </c>
       <c r="D14" s="7">
@@ -1510,22 +1507,22 @@
       <c r="E14" s="8">
         <v>46244</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="8">
         <v>46248</v>
       </c>
       <c r="G14" s="7">
-        <v>22187</v>
-      </c>
-      <c r="H14" s="10">
-        <v>46235</v>
+        <v>21381</v>
+      </c>
+      <c r="H14" s="9">
+        <v>46204</v>
       </c>
       <c r="I14" s="8">
         <v>46244</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1534,9 +1531,9 @@
         <v>11</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="11">
+        <v>16</v>
+      </c>
+      <c r="C15" s="7">
         <v>2026</v>
       </c>
       <c r="D15" s="7">
@@ -1545,22 +1542,22 @@
       <c r="E15" s="8">
         <v>46244</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="8">
         <v>46248</v>
       </c>
       <c r="G15" s="7">
-        <v>22225</v>
-      </c>
-      <c r="H15" s="10">
+        <v>22472</v>
+      </c>
+      <c r="H15" s="9">
         <v>46235</v>
       </c>
       <c r="I15" s="8">
         <v>46244</v>
       </c>
-      <c r="J15" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" s="11" t="s">
+      <c r="J15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1569,9 +1566,9 @@
         <v>11</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="11">
+        <v>18</v>
+      </c>
+      <c r="C16" s="7">
         <v>2026</v>
       </c>
       <c r="D16" s="7">
@@ -1580,22 +1577,22 @@
       <c r="E16" s="8">
         <v>46244</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="8">
         <v>46248</v>
       </c>
       <c r="G16" s="7">
-        <v>22233</v>
-      </c>
-      <c r="H16" s="10">
+        <v>22267</v>
+      </c>
+      <c r="H16" s="9">
         <v>46235</v>
       </c>
       <c r="I16" s="8">
         <v>46244</v>
       </c>
-      <c r="J16" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" s="11" t="s">
+      <c r="J16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1606,7 +1603,7 @@
       <c r="B17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="7">
         <v>2026</v>
       </c>
       <c r="D17" s="7">
@@ -1615,22 +1612,22 @@
       <c r="E17" s="8">
         <v>46244</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="8">
         <v>46248</v>
       </c>
       <c r="G17" s="7">
-        <v>22267</v>
-      </c>
-      <c r="H17" s="10">
+        <v>22311</v>
+      </c>
+      <c r="H17" s="9">
         <v>46235</v>
       </c>
       <c r="I17" s="8">
         <v>46244</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K17" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1639,9 +1636,9 @@
         <v>11</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="11">
+        <v>18</v>
+      </c>
+      <c r="C18" s="7">
         <v>2026</v>
       </c>
       <c r="D18" s="7">
@@ -1650,22 +1647,22 @@
       <c r="E18" s="8">
         <v>46244</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="8">
         <v>46248</v>
       </c>
       <c r="G18" s="7">
-        <v>22272</v>
-      </c>
-      <c r="H18" s="10">
+        <v>22431</v>
+      </c>
+      <c r="H18" s="9">
         <v>46235</v>
       </c>
       <c r="I18" s="8">
         <v>46244</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="J18" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="K18" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1676,7 +1673,7 @@
       <c r="B19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="7">
         <v>2026</v>
       </c>
       <c r="D19" s="7">
@@ -1685,22 +1682,22 @@
       <c r="E19" s="8">
         <v>46244</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="8">
         <v>46248</v>
       </c>
       <c r="G19" s="7">
-        <v>22311</v>
-      </c>
-      <c r="H19" s="10">
+        <v>22452</v>
+      </c>
+      <c r="H19" s="9">
         <v>46235</v>
       </c>
       <c r="I19" s="8">
         <v>46244</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="J19" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="K19" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1709,9 +1706,9 @@
         <v>11</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="11">
+        <v>18</v>
+      </c>
+      <c r="C20" s="7">
         <v>2026</v>
       </c>
       <c r="D20" s="7">
@@ -1720,22 +1717,22 @@
       <c r="E20" s="8">
         <v>46244</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="8">
         <v>46248</v>
       </c>
       <c r="G20" s="7">
-        <v>22362</v>
-      </c>
-      <c r="H20" s="10">
+        <v>22453</v>
+      </c>
+      <c r="H20" s="9">
         <v>46235</v>
       </c>
       <c r="I20" s="8">
         <v>46244</v>
       </c>
-      <c r="J20" s="11" t="s">
+      <c r="J20" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K20" s="11" t="s">
+      <c r="K20" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1746,7 +1743,7 @@
       <c r="B21" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="7">
         <v>2026</v>
       </c>
       <c r="D21" s="7">
@@ -1755,22 +1752,22 @@
       <c r="E21" s="8">
         <v>46244</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="8">
         <v>46248</v>
       </c>
       <c r="G21" s="7">
-        <v>22431</v>
-      </c>
-      <c r="H21" s="10">
+        <v>22454</v>
+      </c>
+      <c r="H21" s="9">
         <v>46235</v>
       </c>
       <c r="I21" s="8">
         <v>46244</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="J21" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="11" t="s">
+      <c r="K21" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1781,7 +1778,7 @@
       <c r="B22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="7">
         <v>2026</v>
       </c>
       <c r="D22" s="7">
@@ -1790,22 +1787,22 @@
       <c r="E22" s="8">
         <v>46244</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="8">
         <v>46248</v>
       </c>
       <c r="G22" s="7">
-        <v>22452</v>
-      </c>
-      <c r="H22" s="10">
+        <v>22455</v>
+      </c>
+      <c r="H22" s="9">
         <v>46235</v>
       </c>
       <c r="I22" s="8">
         <v>46244</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="J22" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K22" s="11" t="s">
+      <c r="K22" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1816,7 +1813,7 @@
       <c r="B23" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="7">
         <v>2026</v>
       </c>
       <c r="D23" s="7">
@@ -1825,22 +1822,22 @@
       <c r="E23" s="8">
         <v>46244</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="8">
         <v>46248</v>
       </c>
       <c r="G23" s="7">
-        <v>22453</v>
-      </c>
-      <c r="H23" s="10">
+        <v>22456</v>
+      </c>
+      <c r="H23" s="9">
         <v>46235</v>
       </c>
       <c r="I23" s="8">
         <v>46244</v>
       </c>
-      <c r="J23" s="11" t="s">
+      <c r="J23" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K23" s="11" t="s">
+      <c r="K23" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1851,7 +1848,7 @@
       <c r="B24" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="7">
         <v>2026</v>
       </c>
       <c r="D24" s="7">
@@ -1860,22 +1857,22 @@
       <c r="E24" s="8">
         <v>46244</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="8">
         <v>46248</v>
       </c>
       <c r="G24" s="7">
-        <v>22454</v>
-      </c>
-      <c r="H24" s="10">
+        <v>22457</v>
+      </c>
+      <c r="H24" s="9">
         <v>46235</v>
       </c>
       <c r="I24" s="8">
         <v>46244</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="J24" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K24" s="11" t="s">
+      <c r="K24" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1886,7 +1883,7 @@
       <c r="B25" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="7">
         <v>2026</v>
       </c>
       <c r="D25" s="7">
@@ -1895,22 +1892,22 @@
       <c r="E25" s="8">
         <v>46244</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="8">
         <v>46248</v>
       </c>
       <c r="G25" s="7">
-        <v>22455</v>
-      </c>
-      <c r="H25" s="10">
+        <v>22458</v>
+      </c>
+      <c r="H25" s="9">
         <v>46235</v>
       </c>
       <c r="I25" s="8">
         <v>46244</v>
       </c>
-      <c r="J25" s="11" t="s">
+      <c r="J25" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K25" s="11" t="s">
+      <c r="K25" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1921,7 +1918,7 @@
       <c r="B26" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="7">
         <v>2026</v>
       </c>
       <c r="D26" s="7">
@@ -1930,22 +1927,22 @@
       <c r="E26" s="8">
         <v>46244</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="8">
         <v>46248</v>
       </c>
       <c r="G26" s="7">
-        <v>22456</v>
-      </c>
-      <c r="H26" s="10">
+        <v>22466</v>
+      </c>
+      <c r="H26" s="9">
         <v>46235</v>
       </c>
       <c r="I26" s="8">
         <v>46244</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="J26" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K26" s="11" t="s">
+      <c r="K26" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1956,7 +1953,7 @@
       <c r="B27" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="7">
         <v>2026</v>
       </c>
       <c r="D27" s="7">
@@ -1965,22 +1962,22 @@
       <c r="E27" s="8">
         <v>46244</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="8">
         <v>46248</v>
       </c>
       <c r="G27" s="7">
-        <v>22457</v>
-      </c>
-      <c r="H27" s="10">
+        <v>22469</v>
+      </c>
+      <c r="H27" s="9">
         <v>46235</v>
       </c>
       <c r="I27" s="8">
         <v>46244</v>
       </c>
-      <c r="J27" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K27" s="11" t="s">
+      <c r="J27" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1991,7 +1988,7 @@
       <c r="B28" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="7">
         <v>2026</v>
       </c>
       <c r="D28" s="7">
@@ -2000,22 +1997,22 @@
       <c r="E28" s="8">
         <v>46244</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="8">
         <v>46248</v>
       </c>
       <c r="G28" s="7">
-        <v>22458</v>
-      </c>
-      <c r="H28" s="10">
+        <v>22473</v>
+      </c>
+      <c r="H28" s="9">
         <v>46235</v>
       </c>
       <c r="I28" s="8">
         <v>46244</v>
       </c>
-      <c r="J28" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K28" s="11" t="s">
+      <c r="J28" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K28" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2026,7 +2023,7 @@
       <c r="B29" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="7">
         <v>2026</v>
       </c>
       <c r="D29" s="7">
@@ -2035,22 +2032,22 @@
       <c r="E29" s="8">
         <v>46244</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="8">
         <v>46248</v>
       </c>
       <c r="G29" s="7">
-        <v>22466</v>
-      </c>
-      <c r="H29" s="10">
+        <v>22485</v>
+      </c>
+      <c r="H29" s="9">
         <v>46235</v>
       </c>
       <c r="I29" s="8">
         <v>46244</v>
       </c>
-      <c r="J29" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K29" s="11" t="s">
+      <c r="J29" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K29" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2061,7 +2058,7 @@
       <c r="B30" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="7">
         <v>2026</v>
       </c>
       <c r="D30" s="7">
@@ -2070,22 +2067,22 @@
       <c r="E30" s="8">
         <v>46244</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="8">
         <v>46248</v>
       </c>
       <c r="G30" s="7">
-        <v>22469</v>
-      </c>
-      <c r="H30" s="10">
+        <v>22487</v>
+      </c>
+      <c r="H30" s="9">
         <v>46235</v>
       </c>
       <c r="I30" s="8">
         <v>46244</v>
       </c>
-      <c r="J30" s="11" t="s">
+      <c r="J30" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K30" s="11" t="s">
+      <c r="K30" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2094,9 +2091,9 @@
         <v>11</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="11">
+        <v>18</v>
+      </c>
+      <c r="C31" s="7">
         <v>2026</v>
       </c>
       <c r="D31" s="7">
@@ -2105,22 +2102,22 @@
       <c r="E31" s="8">
         <v>46244</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="8">
         <v>46248</v>
       </c>
       <c r="G31" s="7">
-        <v>22472</v>
-      </c>
-      <c r="H31" s="10">
+        <v>22500</v>
+      </c>
+      <c r="H31" s="9">
         <v>46235</v>
       </c>
       <c r="I31" s="8">
         <v>46244</v>
       </c>
-      <c r="J31" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K31" s="11" t="s">
+      <c r="J31" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2129,9 +2126,9 @@
         <v>11</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="11">
+        <v>20</v>
+      </c>
+      <c r="C32" s="7">
         <v>2026</v>
       </c>
       <c r="D32" s="7">
@@ -2140,22 +2137,22 @@
       <c r="E32" s="8">
         <v>46244</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="8">
         <v>46248</v>
       </c>
       <c r="G32" s="7">
-        <v>22473</v>
-      </c>
-      <c r="H32" s="10">
+        <v>22272</v>
+      </c>
+      <c r="H32" s="9">
         <v>46235</v>
       </c>
       <c r="I32" s="8">
         <v>46244</v>
       </c>
-      <c r="J32" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K32" s="11" t="s">
+      <c r="J32" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K32" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2164,9 +2161,9 @@
         <v>11</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="11">
+        <v>20</v>
+      </c>
+      <c r="C33" s="7">
         <v>2026</v>
       </c>
       <c r="D33" s="7">
@@ -2175,22 +2172,22 @@
       <c r="E33" s="8">
         <v>46244</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F33" s="8">
         <v>46248</v>
       </c>
       <c r="G33" s="7">
-        <v>22485</v>
-      </c>
-      <c r="H33" s="10">
+        <v>22517</v>
+      </c>
+      <c r="H33" s="9">
         <v>46235</v>
       </c>
       <c r="I33" s="8">
         <v>46244</v>
       </c>
-      <c r="J33" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K33" s="11" t="s">
+      <c r="J33" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2199,9 +2196,9 @@
         <v>11</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="11">
+        <v>13</v>
+      </c>
+      <c r="C34" s="7">
         <v>2026</v>
       </c>
       <c r="D34" s="7">
@@ -2210,22 +2207,22 @@
       <c r="E34" s="8">
         <v>46244</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="8">
         <v>46248</v>
       </c>
       <c r="G34" s="7">
-        <v>22487</v>
-      </c>
-      <c r="H34" s="10">
-        <v>46235</v>
+        <v>20268</v>
+      </c>
+      <c r="H34" s="9">
+        <v>46204</v>
       </c>
       <c r="I34" s="8">
         <v>46244</v>
       </c>
-      <c r="J34" s="11" t="s">
+      <c r="J34" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K34" s="11" t="s">
+      <c r="K34" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2234,9 +2231,9 @@
         <v>11</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="11">
+        <v>17</v>
+      </c>
+      <c r="C35" s="7">
         <v>2026</v>
       </c>
       <c r="D35" s="7">
@@ -2245,22 +2242,22 @@
       <c r="E35" s="8">
         <v>46244</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="8">
         <v>46248</v>
       </c>
       <c r="G35" s="7">
-        <v>22500</v>
-      </c>
-      <c r="H35" s="10">
-        <v>46235</v>
+        <v>21202</v>
+      </c>
+      <c r="H35" s="9">
+        <v>46204</v>
       </c>
       <c r="I35" s="8">
         <v>46244</v>
       </c>
-      <c r="J35" s="11" t="s">
+      <c r="J35" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K35" s="11" t="s">
+      <c r="K35" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2269,9 +2266,9 @@
         <v>11</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="11">
+        <v>17</v>
+      </c>
+      <c r="C36" s="7">
         <v>2026</v>
       </c>
       <c r="D36" s="7">
@@ -2280,22 +2277,22 @@
       <c r="E36" s="8">
         <v>46244</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F36" s="8">
         <v>46248</v>
       </c>
       <c r="G36" s="7">
-        <v>22517</v>
-      </c>
-      <c r="H36" s="10">
-        <v>46235</v>
+        <v>21488</v>
+      </c>
+      <c r="H36" s="9">
+        <v>46204</v>
       </c>
       <c r="I36" s="8">
         <v>46244</v>
       </c>
-      <c r="J36" s="11" t="s">
+      <c r="J36" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K36" s="11" t="s">
+      <c r="K36" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2304,9 +2301,9 @@
         <v>11</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" s="11">
+        <v>17</v>
+      </c>
+      <c r="C37" s="7">
         <v>2026</v>
       </c>
       <c r="D37" s="7">
@@ -2315,22 +2312,22 @@
       <c r="E37" s="8">
         <v>46244</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="8">
         <v>46248</v>
       </c>
       <c r="G37" s="7">
-        <v>22555</v>
-      </c>
-      <c r="H37" s="10">
-        <v>46235</v>
+        <v>21608</v>
+      </c>
+      <c r="H37" s="9">
+        <v>46204</v>
       </c>
       <c r="I37" s="8">
         <v>46244</v>
       </c>
-      <c r="J37" s="11" t="s">
+      <c r="J37" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K37" s="11" t="s">
+      <c r="K37" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2339,9 +2336,9 @@
         <v>11</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" s="11">
+        <v>12</v>
+      </c>
+      <c r="C38" s="7">
         <v>2026</v>
       </c>
       <c r="D38" s="7">
@@ -2350,22 +2347,22 @@
       <c r="E38" s="8">
         <v>46244</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F38" s="8">
         <v>46248</v>
       </c>
       <c r="G38" s="7">
-        <v>22562</v>
-      </c>
-      <c r="H38" s="10">
+        <v>22362</v>
+      </c>
+      <c r="H38" s="9">
         <v>46235</v>
       </c>
       <c r="I38" s="8">
         <v>46244</v>
       </c>
-      <c r="J38" s="11" t="s">
+      <c r="J38" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K38" s="11" t="s">
+      <c r="K38" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2374,7 +2371,11 @@
       <c r="E39" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{D9E61C76-556F-49C0-B235-601DEEC60B9C}"/>
+  <autoFilter ref="A1:K38" xr:uid="{D9E61C76-556F-49C0-B235-601DEEC60B9C}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K38">
+      <sortCondition ref="B1:B38"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -2438,7 +2439,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="7">
         <v>2026</v>
@@ -2449,22 +2450,22 @@
       <c r="E2" s="8">
         <v>46244</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="8">
         <v>46248</v>
       </c>
       <c r="G2" s="7">
-        <v>21551</v>
-      </c>
-      <c r="H2" s="10">
-        <v>46204</v>
+        <v>21980</v>
+      </c>
+      <c r="H2" s="9">
+        <v>46235</v>
       </c>
       <c r="I2" s="8">
         <v>46244</v>
       </c>
-      <c r="J2" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="11" t="s">
+      <c r="J2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2484,22 +2485,22 @@
       <c r="E3" s="8">
         <v>46244</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="8">
         <v>46248</v>
       </c>
       <c r="G3" s="7">
-        <v>21980</v>
-      </c>
-      <c r="H3" s="10">
+        <v>22132</v>
+      </c>
+      <c r="H3" s="9">
         <v>46235</v>
       </c>
       <c r="I3" s="8">
         <v>46244</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2519,22 +2520,22 @@
       <c r="E4" s="8">
         <v>46244</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <v>46248</v>
       </c>
       <c r="G4" s="7">
-        <v>22123</v>
-      </c>
-      <c r="H4" s="10">
-        <v>46235</v>
+        <v>21551</v>
+      </c>
+      <c r="H4" s="9">
+        <v>46204</v>
       </c>
       <c r="I4" s="8">
         <v>46244</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2543,7 +2544,7 @@
         <v>25</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="7">
         <v>2026</v>
@@ -2554,22 +2555,22 @@
       <c r="E5" s="8">
         <v>46244</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>46248</v>
       </c>
       <c r="G5" s="7">
-        <v>22132</v>
-      </c>
-      <c r="H5" s="10">
+        <v>22123</v>
+      </c>
+      <c r="H5" s="9">
         <v>46235</v>
       </c>
       <c r="I5" s="8">
         <v>46244</v>
       </c>
-      <c r="J5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="11" t="s">
+      <c r="J5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2589,22 +2590,22 @@
       <c r="E6" s="8">
         <v>46244</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <v>46248</v>
       </c>
       <c r="G6" s="7">
         <v>22229</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <v>46235</v>
       </c>
       <c r="I6" s="8">
         <v>46244</v>
       </c>
-      <c r="J6" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="11" t="s">
+      <c r="J6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2624,22 +2625,22 @@
       <c r="E7" s="8">
         <v>46244</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>46248</v>
       </c>
       <c r="G7" s="7">
         <v>22278</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <v>46235</v>
       </c>
       <c r="I7" s="8">
         <v>46244</v>
       </c>
-      <c r="J7" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="11" t="s">
+      <c r="J7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2656,7 +2657,11 @@
       <c r="E10" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{CC608613-ED42-4C79-AF4F-9317D29BA8D9}"/>
+  <autoFilter ref="A1:K1" xr:uid="{CC608613-ED42-4C79-AF4F-9317D29BA8D9}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K7">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>